--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>C25819</t>
+          <t>C25792</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LPS22HBTR barometer</t>
+          <t>LPS22HHTR barometer</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>C94049</t>
+          <t>C2827824</t>
         </is>
       </c>
     </row>

--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WS2812B-2020 RGB LED</t>
+          <t>XL-2020RGBC-WS2812B RGB LED</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C965555</t>
+          <t>C5349955</t>
         </is>
       </c>
     </row>
@@ -788,188 +788,188 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RB521S30 Schottky SOD-523</t>
+          <t>USB-C receptacle TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SOD-523</t>
+          <t>USB-C 16P SMD</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>C8523</t>
+          <t>C165948</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>USB-C receptacle TYPE-C-31-M-12</t>
+          <t>JST SH 8P side entry</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2,J6</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>USB-C 16P SMD</t>
+          <t>SMD,P=1mm,Side entry (JST SH 8P)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>C165948</t>
+          <t>C160407</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>JST SH 8P side entry</t>
+          <t>JST SH 4P 1.0 mm side entry</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>J2,J6</t>
+          <t>J3,J4,J5</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=1mm,Side entry (JST SH 8P)</t>
+          <t>SMD,P=1mm,Side entry (JST SH 4P)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>C160407</t>
+          <t>C160404</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>JST SH 4P 1.0 mm side entry</t>
+          <t>2.2uH 0805 power inductor</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>J3,J4,J5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SMD,P=1mm,Side entry (JST SH 4P)</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>C160404</t>
+          <t>C55755</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2.2uH 0805 power inductor</t>
+          <t>10nH 5% 0402</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>C55755</t>
+          <t>C77103</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10nH 5% 0402</t>
+          <t>SWPA5040S220MT 22uH 1.5A 5x5x4</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD 5x5 (SWPA5040S)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>C77103</t>
+          <t>C68434</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SWPA5040S220MT 22uH 1.5A 5x5x4</t>
+          <t>AO3401A P-MOSFET SOT-23</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SMD 5x5 (SWPA5040S)</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>C68434</t>
+          <t>C15127</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AO3401A P-MOSFET SOT-23</t>
+          <t>100k 1% 0402</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>R2,R4,R8,R10,R11</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>C15127</t>
+          <t>C25741</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>100k 1% 0402</t>
+          <t>287k 1% 0402</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>R2,R4,R8,R10,R11</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>C25741</t>
+          <t>C42921050</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>287k 1% 0402</t>
+          <t>10k 1% 0402</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R9,R14,R37,R38</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>C42921050</t>
+          <t>C25744</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10k 1% 0402</t>
+          <t>5.1k 1% 0402</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>R9,R14,R37,R38</t>
+          <t>R12,R13</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25905</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>5.1k 1% 0402</t>
+          <t>2.2k 1% 0402</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>R12,R13</t>
+          <t>R15,R16</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>C25905</t>
+          <t>C25879</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2.2k 1% 0402</t>
+          <t>4.7k 1% 0402</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>R15,R16</t>
+          <t>R17,R18</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>C25879</t>
+          <t>C25900</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>4.7k 1% 0402</t>
+          <t>100R 1% 0402</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>R17,R18</t>
+          <t>R20,R21,R22,R23,R24,R25,R26,R27,R28</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>C25900</t>
+          <t>C25076</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>100R 1% 0402</t>
+          <t>0R 0402</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>R20,R21,R22,R23,R24,R25,R26,R27,R28</t>
+          <t>R34,R49</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>C25076</t>
+          <t>C17168</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>0R 0402</t>
+          <t>33R 0402</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>C17168</t>
+          <t>C25105</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>33R 0402</t>
+          <t>47k 1% 0402</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>C25105</t>
+          <t>C25792</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>47k 1% 0402</t>
+          <t>15k 1% 0402</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>C25792</t>
+          <t>C25756</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>15k 1% 0402</t>
+          <t>1k 1% 0402</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>C25756</t>
+          <t>C11702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1k 1% 0402</t>
+          <t>470k 1% 0402</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25790</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>470k 1% 0402</t>
+          <t>200k 1% 0402</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1243,269 +1243,247 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>C25790</t>
+          <t>C25764</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>200k 1% 0402</t>
+          <t>LSM6DSV16XTR IMU</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>LGA-14 (2.5x3)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>C25764</t>
+          <t>C5267406</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LSM6DSV16XTR IMU</t>
+          <t>STM32WB55CGU6</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>LGA-14 (2.5x3)</t>
+          <t>UFQFPN-48 (7x7)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>C5267406</t>
+          <t>C404023</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>STM32WB55CGU6</t>
+          <t>IIS2MDCTR magnetometer</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UFQFPN-48 (7x7)</t>
+          <t>LGA-12 (2x2)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>C404023</t>
+          <t>C2655002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IIS2MDCTR magnetometer</t>
+          <t>LPS22HHTR barometer</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LGA-12 (2x2)</t>
+          <t>HLGA-10 (2x2)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>C2655002</t>
+          <t>C2827824</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LPS22HHTR barometer</t>
+          <t>LD39130SPUR LDO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>HLGA-10 (2x2)</t>
+          <t>DFN-6 (1.2x1.3)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>C2827824</t>
+          <t>C2798213</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LD39130SPUR LDO</t>
+          <t>USBLC6-2SC6 ESD</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>DFN-6 (1.2x1.3)</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>C2798213</t>
+          <t>C7519</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>USBLC6-2SC6 ESD</t>
+          <t>MLPF-WB55-01E3 RF filter</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>CSP-6 (1.0x1.6)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>C7519</t>
+          <t>C2651048</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MLPF-WB55-01E3 RF filter</t>
+          <t>W25Q128JVPIQ 128 Mbit SPI flash WSON-8</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CSP-6 (1.0x1.6)</t>
+          <t>WSON-8 (6x5)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>C2651048</t>
+          <t>C190862</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>W25Q128JVPIQ 128 Mbit SPI flash WSON-8</t>
+          <t>LDK130PU-R adjustable LDO DFN-6</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>WSON-8 (6x5)</t>
+          <t>DFN-6 (1.2x1.3)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>C190862</t>
+          <t>C157446</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LDK130PU-R adjustable LDO DFN-6</t>
+          <t>LM5166DRCT buck 3-65V 0.5A VSON-10</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>DFN-6 (1.2x1.3)</t>
+          <t>VSON-10 (3x3)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>C157446</t>
+          <t>C181495</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LM5166DRCT buck 3-65V 0.5A VSON-10</t>
+          <t>32MHz crystal 8pF 2016</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VSON-10 (3x3)</t>
+          <t>SMD2016-4P</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>C181495</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>32MHz crystal 8pF 2016</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>SMD2016-4P</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>C843260</t>
         </is>

--- a/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
+++ b/00 - Docs/00 - FC_Docs/ACwing_FC_A_BoM_JLCPCB.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>C1,C12,C14,C15,C16,C17,C19,C21,C23,C24,C25,C26,C28,C39,C40,C41,C42,C45</t>
+          <t>C1,C12,C14,C15,C16,C17,C19,C21,C23,C24,C25,C26,C28,C39,C40,C41,C42,C45,C50</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>R34,R49</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1470,20 +1470,42 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>SN74LV1T34DCKR level-shift buffer SC-70-5</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>SC-70-5 (SOT-353)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>C78541</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>32MHz crystal 8pF 2016</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>SMD2016-4P</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>C843260</t>
         </is>
